--- a/Datos 04.01 - D.xlsx
+++ b/Datos 04.01 - D.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Cursos\Introduccion a la Ciencia de Datos\GitHub\EP1053\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BB5BED-7D81-4E12-BC16-27EB21782CB6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22608" windowHeight="8604" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Empleados" sheetId="1" r:id="rId1"/>
     <sheet name="Areas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>APELLIDOS</t>
   </si>
@@ -202,12 +203,18 @@
   </si>
   <si>
     <t>Patricia Sierra</t>
+  </si>
+  <si>
+    <t>FECHA_NACIMIENTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -237,9 +244,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,15 +529,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -540,8 +551,11 @@
       <c r="D1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -554,8 +568,11 @@
       <c r="D2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="2">
+        <v>26313</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -568,8 +585,11 @@
       <c r="D3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="2">
+        <v>33136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -582,8 +602,11 @@
       <c r="D4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="2">
+        <v>21939</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -596,8 +619,11 @@
       <c r="D5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="2">
+        <v>26922</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -610,8 +636,11 @@
       <c r="D6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="2">
+        <v>33726</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -624,8 +653,11 @@
       <c r="D7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="2">
+        <v>27024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -638,8 +670,11 @@
       <c r="D8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="2">
+        <v>24535</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -652,8 +687,11 @@
       <c r="D9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="2">
+        <v>26672</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -666,8 +704,11 @@
       <c r="D10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="2">
+        <v>29644</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -680,8 +721,11 @@
       <c r="D11" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="2">
+        <v>22509</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -694,8 +738,11 @@
       <c r="D12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="2">
+        <v>22478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -708,8 +755,11 @@
       <c r="D13" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="2">
+        <v>23884</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -722,8 +772,11 @@
       <c r="D14" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="2">
+        <v>30848</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -736,8 +789,11 @@
       <c r="D15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="2">
+        <v>25336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -749,6 +805,9 @@
       </c>
       <c r="D16" t="s">
         <v>56</v>
+      </c>
+      <c r="E16" s="2">
+        <v>25157</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +817,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
